--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$174</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5436" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,16 +549,138 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis</t>
   </si>
   <si>
-    <t>SubstanceAdministration.negationInd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.text</t>
+    <t>SubstanceAdministration.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
   </si>
   <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.negationInd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.text</t>
+  </si>
+  <si>
     <t>Partie narrative de l’entrée</t>
   </si>
   <si>
@@ -711,123 +833,34 @@
     <t>SubstanceAdministration.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>active</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>SubstanceAdministration.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>SubstanceAdministration.effectiveTime</t>
@@ -1779,7 +1812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK163"/>
+  <dimension ref="A1:AK174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.5234375" customWidth="true" bestFit="true"/>
@@ -5003,7 +5036,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>166</v>
       </c>
@@ -5022,7 +5055,7 @@
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -5218,7 +5251,9 @@
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E34" s="2"/>
+      <c r="E34" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5235,10 +5270,12 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5264,13 +5301,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -5288,7 +5323,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5317,7 +5352,9 @@
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5334,12 +5371,12 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5389,7 +5426,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5407,7 +5444,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>177</v>
       </c>
@@ -5419,16 +5456,16 @@
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5437,11 +5474,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5468,11 +5505,13 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -5490,7 +5529,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5510,17 +5549,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5538,11 +5577,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5569,11 +5608,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5591,7 +5632,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5611,17 +5652,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5639,11 +5680,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5694,7 +5735,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5712,19 +5753,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5733,7 +5774,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5742,11 +5783,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5773,11 +5814,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5824,26 +5867,24 @@
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E40" t="s" s="2">
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
@@ -5927,9 +5968,7 @@
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5946,11 +5985,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5977,11 +6016,13 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5999,7 +6040,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6019,16 +6060,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6045,10 +6088,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6074,29 +6119,31 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6116,21 +6163,23 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -6142,17 +6191,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L43" t="s" s="2">
         <v>207</v>
       </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>74</v>
@@ -6201,46 +6246,46 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6249,11 +6294,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6304,13 +6349,13 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>74</v>
@@ -6324,18 +6369,16 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6352,12 +6395,10 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6407,7 +6448,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6427,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6453,14 +6494,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6486,11 +6525,13 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6508,7 +6549,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6528,10 +6569,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6629,17 +6670,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -6661,7 +6702,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6673,7 +6714,7 @@
         <v>74</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>74</v>
@@ -6688,13 +6729,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6712,7 +6751,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6732,23 +6771,23 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6760,11 +6799,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6815,7 +6854,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6835,23 +6874,23 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6863,11 +6902,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6894,13 +6933,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6918,7 +6955,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6938,23 +6975,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6966,11 +7003,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7021,7 +7058,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7041,23 +7078,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -7069,11 +7106,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7100,13 +7137,11 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -7124,7 +7159,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7144,10 +7179,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7170,12 +7205,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="L53" s="2"/>
-      <c r="M53" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7201,13 +7234,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7225,7 +7256,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7245,10 +7276,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7273,11 +7304,15 @@
       <c r="K54" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L54" s="2"/>
+      <c r="L54" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="M54" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>74</v>
@@ -7326,55 +7361,55 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="B55" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
@@ -7465,7 +7500,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7477,11 +7512,11 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7532,59 +7567,59 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" t="s" s="2">
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7611,13 +7646,11 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7635,44 +7668,46 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F58" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>74</v>
@@ -7681,13 +7716,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>267</v>
+        <v>86</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7714,13 +7747,11 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7738,13 +7769,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>265</v>
+        <v>89</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -7758,16 +7789,18 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
@@ -7784,10 +7817,12 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+      <c r="M59" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7798,7 +7833,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7813,11 +7848,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7835,7 +7872,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7855,21 +7892,23 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7881,10 +7920,12 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>272</v>
+        <v>112</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
+      <c r="M60" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7934,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7952,26 +7993,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>74</v>
@@ -7980,13 +8023,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8013,11 +8054,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>275</v>
+        <v>74</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -8035,7 +8078,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8053,26 +8096,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>74</v>
@@ -8081,13 +8126,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8114,11 +8157,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>279</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -8136,13 +8181,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -8154,26 +8199,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -8182,13 +8229,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8239,7 +8284,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8259,10 +8304,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8285,10 +8330,12 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
+      <c r="M64" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8338,7 +8385,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>283</v>
+        <v>196</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8358,10 +8405,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8384,10 +8431,12 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
+      <c r="M65" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8437,7 +8486,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8457,21 +8506,23 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8483,10 +8534,12 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>269</v>
+        <v>202</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
+      <c r="M66" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8512,11 +8565,13 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>287</v>
+        <v>74</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8534,7 +8589,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>286</v>
+        <v>204</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8554,21 +8609,23 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="F67" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>74</v>
@@ -8580,13 +8637,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>290</v>
+        <v>208</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8637,13 +8692,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>288</v>
+        <v>209</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8657,23 +8712,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8685,11 +8740,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8716,11 +8771,13 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
@@ -8738,13 +8795,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8756,12 +8813,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8769,13 +8826,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
@@ -8784,11 +8841,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L69" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="M69" t="s" s="2">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8839,7 +8898,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>93</v>
+        <v>276</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8859,10 +8918,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8885,12 +8944,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8916,13 +8973,11 @@
         <v>74</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>74</v>
+        <v>281</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8940,7 +8995,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8952,7 +9007,7 @@
         <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>74</v>
@@ -8960,18 +9015,16 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
@@ -8988,12 +9041,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9019,11 +9070,13 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -9041,7 +9094,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>89</v>
+        <v>282</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9059,20 +9112,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
@@ -9080,7 +9131,7 @@
         <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>74</v>
@@ -9089,11 +9140,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L72" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="M72" t="s" s="2">
-        <v>103</v>
+        <v>285</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9120,13 +9173,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9144,7 +9195,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9162,28 +9213,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -9192,11 +9241,13 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L73" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="M73" t="s" s="2">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9223,13 +9274,11 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9247,13 +9296,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -9265,28 +9314,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
@@ -9295,11 +9342,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="M74" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9308,7 +9357,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -9350,7 +9399,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9370,20 +9419,18 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
@@ -9398,12 +9445,10 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9453,7 +9498,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9473,10 +9518,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9487,7 +9532,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -9499,12 +9544,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9554,13 +9597,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>125</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9574,10 +9617,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9600,7 +9643,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9611,7 +9654,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>301</v>
+        <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>74</v>
@@ -9629,11 +9672,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9651,7 +9694,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9671,10 +9714,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9697,10 +9740,14 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9750,7 +9797,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -9770,16 +9817,18 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
@@ -9796,10 +9845,12 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>306</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9825,13 +9876,11 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9849,7 +9898,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>305</v>
+        <v>89</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9869,10 +9918,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9895,10 +9944,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>308</v>
+        <v>91</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9948,7 +9999,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>307</v>
+        <v>93</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9968,10 +10019,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9982,7 +10033,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9994,10 +10045,12 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10047,19 +10100,19 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>309</v>
+        <v>97</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>74</v>
@@ -10067,21 +10120,23 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>74</v>
@@ -10093,10 +10148,12 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10122,13 +10179,11 @@
         <v>74</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -10146,13 +10201,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -10166,21 +10221,23 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -10192,10 +10249,12 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10245,13 +10304,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>313</v>
+        <v>104</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -10265,21 +10324,23 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -10291,10 +10352,12 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>316</v>
+        <v>107</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10344,13 +10407,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>315</v>
+        <v>109</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -10364,24 +10427,26 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>74</v>
@@ -10390,10 +10455,12 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>318</v>
+        <v>112</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10401,7 +10468,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -10431,23 +10498,25 @@
         <v>74</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>317</v>
+        <v>115</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10461,20 +10530,20 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>75</v>
@@ -10489,12 +10558,12 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M86" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10544,13 +10613,13 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>317</v>
+        <v>119</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>74</v>
@@ -10564,23 +10633,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10592,11 +10659,11 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10623,11 +10690,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10645,13 +10714,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10665,10 +10734,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10679,7 +10748,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10691,12 +10760,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10704,7 +10771,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>74</v>
+        <v>312</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -10722,13 +10789,11 @@
         <v>74</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10746,13 +10811,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10766,10 +10831,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10777,7 +10842,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>75</v>
@@ -10792,12 +10857,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>95</v>
+        <v>315</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10847,10 +10910,10 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>75</v>
@@ -10859,7 +10922,7 @@
         <v>74</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>74</v>
@@ -10867,18 +10930,16 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
@@ -10895,12 +10956,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>85</v>
+        <v>317</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10926,11 +10985,13 @@
         <v>74</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>74</v>
@@ -10948,7 +11009,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10968,23 +11029,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>74</v>
@@ -10996,12 +11055,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11051,13 +11108,13 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>74</v>
@@ -11071,23 +11128,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -11099,12 +11154,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>321</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11154,13 +11207,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -11174,23 +11227,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -11202,12 +11253,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11215,7 +11264,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>74</v>
@@ -11257,13 +11306,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>115</v>
+        <v>322</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -11277,23 +11326,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -11305,12 +11352,10 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>102</v>
+        <v>325</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11360,13 +11405,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>119</v>
+        <v>324</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11380,10 +11425,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11406,12 +11451,10 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="L95" s="2"/>
-      <c r="M95" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11461,7 +11504,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>125</v>
+        <v>326</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11481,10 +11524,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11492,13 +11535,13 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>74</v>
@@ -11507,7 +11550,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11521,7 +11564,7 @@
         <v>74</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>343</v>
+        <v>74</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>74</v>
@@ -11536,35 +11579,35 @@
         <v>74</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y96" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z96" t="s" s="2">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>74</v>
@@ -11578,12 +11621,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
@@ -11604,12 +11649,12 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11659,13 +11704,13 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>74</v>
@@ -11679,16 +11724,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
@@ -11705,16 +11752,16 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>353</v>
+        <v>74</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
@@ -11736,13 +11783,11 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11760,7 +11805,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11780,10 +11825,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11794,7 +11839,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11806,10 +11851,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11859,13 +11906,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>357</v>
+        <v>93</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11879,10 +11926,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11905,10 +11952,12 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11958,7 +12007,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>361</v>
+        <v>97</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11970,7 +12019,7 @@
         <v>74</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>74</v>
@@ -11978,16 +12027,18 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
@@ -12004,10 +12055,12 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>364</v>
+        <v>85</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12033,13 +12086,11 @@
         <v>74</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>74</v>
@@ -12057,7 +12108,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>365</v>
+        <v>89</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12077,16 +12128,18 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
@@ -12103,10 +12156,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>368</v>
+        <v>102</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12156,7 +12211,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12176,16 +12231,18 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E103" s="2"/>
+      <c r="E103" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
@@ -12202,10 +12259,12 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12255,7 +12314,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>373</v>
+        <v>109</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12275,18 +12334,20 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>75</v>
@@ -12301,10 +12362,12 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>376</v>
+        <v>112</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12312,7 +12375,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>74</v>
@@ -12354,7 +12417,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>377</v>
+        <v>115</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12374,18 +12437,20 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F105" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>75</v>
@@ -12400,10 +12465,12 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12453,7 +12520,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>381</v>
+        <v>119</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12473,10 +12540,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12487,7 +12554,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>74</v>
@@ -12499,10 +12566,12 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12552,13 +12621,13 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>385</v>
+        <v>125</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>74</v>
@@ -12572,10 +12641,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12583,7 +12652,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>75</v>
@@ -12598,7 +12667,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12612,7 +12681,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>74</v>
+        <v>354</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -12627,13 +12696,11 @@
         <v>74</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12651,10 +12718,10 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>75</v>
@@ -12671,10 +12738,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12697,10 +12764,12 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>392</v>
+        <v>107</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="M108" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12750,7 +12819,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12770,10 +12839,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12796,14 +12865,16 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>396</v>
+        <v>107</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
+      <c r="M109" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>74</v>
+        <v>364</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
@@ -12849,7 +12920,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12869,10 +12940,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12895,7 +12966,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>400</v>
+        <v>107</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12948,7 +13019,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12968,14 +13039,12 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
@@ -12996,11 +13065,9 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -13051,13 +13118,13 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>74</v>
@@ -13071,18 +13138,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E112" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
@@ -13099,12 +13164,10 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13130,11 +13193,13 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -13152,7 +13217,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>89</v>
+        <v>376</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13172,10 +13237,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13186,7 +13251,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>74</v>
@@ -13198,12 +13263,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>91</v>
+        <v>379</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13253,13 +13316,13 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>93</v>
+        <v>380</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>74</v>
@@ -13273,10 +13336,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>328</v>
+        <v>382</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13299,12 +13362,10 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>95</v>
+        <v>383</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13354,7 +13415,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>97</v>
+        <v>384</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13366,7 +13427,7 @@
         <v>74</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>74</v>
@@ -13374,18 +13435,16 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>330</v>
+        <v>386</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
@@ -13402,12 +13461,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>85</v>
+        <v>387</v>
       </c>
       <c r="L115" s="2"/>
-      <c r="M115" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13433,11 +13490,13 @@
         <v>74</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
@@ -13455,7 +13514,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>89</v>
+        <v>388</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13475,18 +13534,16 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
@@ -13503,12 +13560,10 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13558,7 +13613,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>104</v>
+        <v>392</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13578,18 +13633,16 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E117" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
@@ -13606,12 +13659,10 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>107</v>
+        <v>395</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13661,7 +13712,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>109</v>
+        <v>396</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13681,20 +13732,18 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E118" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>75</v>
@@ -13709,12 +13758,10 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>112</v>
+        <v>399</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13722,7 +13769,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>74</v>
@@ -13764,7 +13811,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>115</v>
+        <v>400</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13784,20 +13831,18 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E119" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>75</v>
@@ -13812,12 +13857,10 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13867,7 +13910,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>119</v>
+        <v>404</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13887,10 +13930,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13901,7 +13944,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>74</v>
@@ -13913,12 +13956,10 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>95</v>
+        <v>407</v>
       </c>
       <c r="L120" s="2"/>
-      <c r="M120" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -13968,13 +14009,13 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>125</v>
+        <v>408</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>74</v>
@@ -13988,10 +14029,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13999,7 +14040,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>75</v>
@@ -14014,7 +14055,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>85</v>
+        <v>411</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14028,7 +14069,7 @@
         <v>74</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>415</v>
+        <v>74</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>74</v>
@@ -14043,11 +14084,13 @@
         <v>74</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -14065,10 +14108,10 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>75</v>
@@ -14085,12 +14128,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
@@ -14111,12 +14156,12 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14166,13 +14211,13 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>74</v>
@@ -14186,16 +14231,18 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
@@ -14212,16 +14259,16 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
-        <v>353</v>
+        <v>74</v>
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
@@ -14243,13 +14290,11 @@
         <v>74</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14267,7 +14312,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14287,10 +14332,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14301,7 +14346,7 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>74</v>
@@ -14313,10 +14358,12 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L124" s="2"/>
-      <c r="M124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14366,13 +14413,13 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>357</v>
+        <v>93</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>74</v>
@@ -14386,10 +14433,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14412,10 +14459,12 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -14465,7 +14514,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>361</v>
+        <v>97</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14477,7 +14526,7 @@
         <v>74</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>74</v>
@@ -14485,16 +14534,18 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F126" t="s" s="2">
         <v>80</v>
       </c>
@@ -14511,10 +14562,12 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>364</v>
+        <v>85</v>
       </c>
       <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
+      <c r="M126" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -14540,13 +14593,11 @@
         <v>74</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>74</v>
@@ -14564,7 +14615,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>365</v>
+        <v>89</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14584,16 +14635,18 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
@@ -14610,10 +14663,12 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>368</v>
+        <v>102</v>
       </c>
       <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
+      <c r="M127" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -14663,7 +14718,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14683,16 +14738,18 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E128" s="2"/>
+      <c r="E128" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F128" t="s" s="2">
         <v>80</v>
       </c>
@@ -14709,10 +14766,12 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -14762,7 +14821,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>373</v>
+        <v>109</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14782,18 +14841,20 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>75</v>
@@ -14808,10 +14869,12 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>424</v>
+        <v>112</v>
       </c>
       <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
+      <c r="M129" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -14819,7 +14882,7 @@
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>74</v>
@@ -14861,7 +14924,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>377</v>
+        <v>115</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14881,18 +14944,20 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E130" s="2"/>
+      <c r="E130" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F130" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>75</v>
@@ -14907,10 +14972,12 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -14960,7 +15027,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>381</v>
+        <v>119</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14980,10 +15047,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14994,7 +15061,7 @@
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>74</v>
@@ -15006,10 +15073,12 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
+      <c r="M131" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -15059,13 +15128,13 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>385</v>
+        <v>125</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>74</v>
@@ -15079,10 +15148,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15090,7 +15159,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>75</v>
@@ -15105,7 +15174,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15119,7 +15188,7 @@
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15134,13 +15203,11 @@
         <v>74</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15158,10 +15225,10 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>75</v>
@@ -15178,10 +15245,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15204,10 +15271,12 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>392</v>
+        <v>107</v>
       </c>
       <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
+      <c r="M133" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -15257,7 +15326,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15277,10 +15346,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15303,14 +15372,16 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>396</v>
+        <v>107</v>
       </c>
       <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
+      <c r="M134" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
-        <v>74</v>
+        <v>364</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
@@ -15356,7 +15427,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15376,10 +15447,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15402,7 +15473,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15455,7 +15526,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15475,14 +15546,12 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>74</v>
       </c>
@@ -15503,11 +15572,9 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15558,13 +15625,13 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>74</v>
@@ -15578,18 +15645,16 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E137" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
@@ -15606,12 +15671,10 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -15637,11 +15700,13 @@
         <v>74</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>74</v>
@@ -15659,7 +15724,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>89</v>
+        <v>376</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15679,10 +15744,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15693,7 +15758,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>74</v>
@@ -15705,12 +15770,10 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>91</v>
+        <v>379</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -15760,13 +15823,13 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>93</v>
+        <v>380</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>74</v>
@@ -15780,10 +15843,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>328</v>
+        <v>382</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15806,12 +15869,10 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>95</v>
+        <v>383</v>
       </c>
       <c r="L139" s="2"/>
-      <c r="M139" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -15861,7 +15922,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>97</v>
+        <v>384</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15873,7 +15934,7 @@
         <v>74</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>74</v>
@@ -15881,18 +15942,16 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>330</v>
+        <v>386</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E140" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
@@ -15909,12 +15968,10 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>85</v>
+        <v>435</v>
       </c>
       <c r="L140" s="2"/>
-      <c r="M140" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -15940,11 +15997,13 @@
         <v>74</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>74</v>
@@ -15962,7 +16021,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>89</v>
+        <v>388</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15982,18 +16041,16 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E141" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
@@ -16010,12 +16067,10 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="L141" s="2"/>
-      <c r="M141" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -16065,7 +16120,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>104</v>
+        <v>392</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16085,18 +16140,16 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E142" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
@@ -16113,12 +16166,10 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>107</v>
+        <v>395</v>
       </c>
       <c r="L142" s="2"/>
-      <c r="M142" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -16168,7 +16219,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>109</v>
+        <v>396</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16188,20 +16239,18 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E143" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>75</v>
@@ -16216,12 +16265,10 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>112</v>
+        <v>399</v>
       </c>
       <c r="L143" s="2"/>
-      <c r="M143" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -16229,7 +16276,7 @@
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S143" t="s" s="2">
         <v>74</v>
@@ -16271,7 +16318,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>115</v>
+        <v>400</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16291,20 +16338,18 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E144" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>75</v>
@@ -16319,12 +16364,10 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="L144" s="2"/>
-      <c r="M144" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -16374,7 +16417,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>119</v>
+        <v>404</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16394,10 +16437,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16408,7 +16451,7 @@
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>74</v>
@@ -16420,12 +16463,10 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>95</v>
+        <v>407</v>
       </c>
       <c r="L145" s="2"/>
-      <c r="M145" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16475,13 +16516,13 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>125</v>
+        <v>408</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>74</v>
@@ -16495,10 +16536,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16506,7 +16547,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>75</v>
@@ -16521,7 +16562,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>85</v>
+        <v>442</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16535,7 +16576,7 @@
         <v>74</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>415</v>
+        <v>74</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>74</v>
@@ -16550,11 +16591,13 @@
         <v>74</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y146" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z146" t="s" s="2">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>74</v>
@@ -16572,10 +16615,10 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>75</v>
@@ -16592,12 +16635,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C147" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="D147" t="s" s="2">
         <v>74</v>
       </c>
@@ -16618,12 +16663,12 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L147" s="2"/>
-      <c r="M147" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -16673,13 +16718,13 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>74</v>
@@ -16696,13 +16741,15 @@
         <v>446</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
@@ -16719,16 +16766,16 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
-        <v>353</v>
+        <v>74</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
@@ -16750,13 +16797,11 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16774,7 +16819,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16797,7 +16842,7 @@
         <v>447</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16808,7 +16853,7 @@
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>74</v>
@@ -16820,10 +16865,12 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
+      <c r="M149" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -16873,13 +16920,13 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>357</v>
+        <v>93</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>74</v>
@@ -16896,7 +16943,7 @@
         <v>448</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16919,10 +16966,12 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="L150" s="2"/>
-      <c r="M150" s="2"/>
+      <c r="M150" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -16972,7 +17021,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>361</v>
+        <v>97</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16984,7 +17033,7 @@
         <v>74</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>74</v>
@@ -16995,13 +17044,15 @@
         <v>449</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E151" s="2"/>
+      <c r="E151" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F151" t="s" s="2">
         <v>80</v>
       </c>
@@ -17018,10 +17069,12 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>364</v>
+        <v>85</v>
       </c>
       <c r="L151" s="2"/>
-      <c r="M151" s="2"/>
+      <c r="M151" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17047,13 +17100,11 @@
         <v>74</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>74</v>
@@ -17071,7 +17122,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>365</v>
+        <v>89</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17094,13 +17145,15 @@
         <v>450</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F152" t="s" s="2">
         <v>80</v>
       </c>
@@ -17117,10 +17170,12 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>451</v>
+        <v>102</v>
       </c>
       <c r="L152" s="2"/>
-      <c r="M152" s="2"/>
+      <c r="M152" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -17170,7 +17225,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17190,16 +17245,18 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E153" s="2"/>
+      <c r="E153" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
@@ -17216,10 +17273,12 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="L153" s="2"/>
-      <c r="M153" s="2"/>
+      <c r="M153" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17269,7 +17328,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>373</v>
+        <v>109</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17289,18 +17348,20 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E154" s="2"/>
+      <c r="E154" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F154" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>75</v>
@@ -17315,10 +17376,12 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>376</v>
+        <v>112</v>
       </c>
       <c r="L154" s="2"/>
-      <c r="M154" s="2"/>
+      <c r="M154" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -17326,7 +17389,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>74</v>
@@ -17368,7 +17431,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>377</v>
+        <v>115</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17388,18 +17451,20 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E155" s="2"/>
+      <c r="E155" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F155" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>75</v>
@@ -17414,10 +17479,12 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="L155" s="2"/>
-      <c r="M155" s="2"/>
+      <c r="M155" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -17467,7 +17534,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>381</v>
+        <v>119</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17487,10 +17554,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17501,7 +17568,7 @@
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>74</v>
@@ -17513,10 +17580,12 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="L156" s="2"/>
-      <c r="M156" s="2"/>
+      <c r="M156" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -17566,13 +17635,13 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>385</v>
+        <v>125</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>74</v>
@@ -17586,10 +17655,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17597,7 +17666,7 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>75</v>
@@ -17612,7 +17681,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17626,7 +17695,7 @@
         <v>74</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>74</v>
@@ -17641,13 +17710,11 @@
         <v>74</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -17665,10 +17732,10 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>75</v>
@@ -17685,10 +17752,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17711,10 +17778,12 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>392</v>
+        <v>107</v>
       </c>
       <c r="L158" s="2"/>
-      <c r="M158" s="2"/>
+      <c r="M158" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -17764,7 +17833,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17784,10 +17853,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17810,14 +17879,16 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>396</v>
+        <v>107</v>
       </c>
       <c r="L159" s="2"/>
-      <c r="M159" s="2"/>
+      <c r="M159" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>74</v>
+        <v>364</v>
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
@@ -17863,7 +17934,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17883,10 +17954,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17909,7 +17980,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -17962,7 +18033,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -17982,10 +18053,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17996,7 +18067,7 @@
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>74</v>
@@ -18008,7 +18079,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>461</v>
+        <v>371</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18061,13 +18132,13 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>460</v>
+        <v>372</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>74</v>
@@ -18081,10 +18152,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>462</v>
+        <v>374</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18095,7 +18166,7 @@
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>74</v>
@@ -18107,7 +18178,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>463</v>
+        <v>375</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18160,13 +18231,13 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>74</v>
@@ -18180,10 +18251,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18194,7 +18265,7 @@
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>74</v>
@@ -18206,7 +18277,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18259,26 +18330,1115 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" hidden="true">
+      <c r="A164" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L164" s="2"/>
+      <c r="M164" s="2"/>
+      <c r="N164" s="2"/>
+      <c r="O164" s="2"/>
+      <c r="P164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" hidden="true">
+      <c r="A165" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AG163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH163" t="s" s="2">
+      <c r="B165" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L165" s="2"/>
+      <c r="M165" s="2"/>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" hidden="true">
+      <c r="A166" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L166" s="2"/>
+      <c r="M166" s="2"/>
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
+      <c r="P166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L167" s="2"/>
+      <c r="M167" s="2"/>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L169" s="2"/>
+      <c r="M169" s="2"/>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
+      <c r="P170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G172" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI163" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK163" t="s" s="2">
+      <c r="H172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L172" s="2"/>
+      <c r="M172" s="2"/>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L173" s="2"/>
+      <c r="M173" s="2"/>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+      <c r="N174" s="2"/>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK174" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK163">
+  <autoFilter ref="A1:AK174">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18288,7 +19448,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI162">
+  <conditionalFormatting sqref="A2:AI173">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5436" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5436" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -813,6 +813,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -7579,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -7587,10 +7591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7616,10 +7620,10 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7668,7 +7672,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7688,10 +7692,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7789,10 +7793,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7833,7 +7837,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7892,10 +7896,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7995,10 +7999,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8098,10 +8102,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8201,10 +8205,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8304,10 +8308,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8405,10 +8409,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8506,10 +8510,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8609,10 +8613,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8712,10 +8716,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8815,10 +8819,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8841,13 +8845,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8898,7 +8902,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8918,10 +8922,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8944,7 +8948,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8977,7 +8981,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8995,7 +8999,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9015,10 +9019,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9041,7 +9045,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -9094,7 +9098,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9114,10 +9118,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9140,13 +9144,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9177,7 +9181,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9195,7 +9199,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9215,10 +9219,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9244,10 +9248,10 @@
         <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9278,7 +9282,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9296,7 +9300,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9342,13 +9346,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9399,7 +9403,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9419,10 +9423,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9445,7 +9449,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9498,7 +9502,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9518,10 +9522,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9544,7 +9548,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9597,7 +9601,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9621,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9643,7 +9647,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9676,25 +9680,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9714,10 +9718,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9740,13 +9744,13 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9797,7 +9801,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -9817,10 +9821,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9918,10 +9922,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10019,10 +10023,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10120,10 +10124,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10221,10 +10225,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10324,10 +10328,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10427,10 +10431,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10530,10 +10534,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10633,10 +10637,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10734,10 +10738,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10771,7 +10775,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -10793,7 +10797,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10811,7 +10815,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10831,10 +10835,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10857,7 +10861,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10910,7 +10914,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -10930,10 +10934,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10956,7 +10960,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -11009,7 +11013,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11029,10 +11033,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11055,7 +11059,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11108,7 +11112,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11128,10 +11132,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11154,7 +11158,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11207,7 +11211,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11231,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11253,7 +11257,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11306,7 +11310,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11326,10 +11330,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11352,7 +11356,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11405,7 +11409,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11425,10 +11429,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11451,7 +11455,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11504,7 +11508,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11524,10 +11528,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11550,7 +11554,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11591,7 +11595,7 @@
         <v>74</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -11601,7 +11605,7 @@
         <v>124</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11621,13 +11625,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>74</v>
@@ -11649,10 +11653,10 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -11704,7 +11708,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11724,10 +11728,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11825,10 +11829,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11926,10 +11930,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12027,10 +12031,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12128,10 +12132,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12231,10 +12235,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12334,10 +12338,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12437,10 +12441,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12540,10 +12544,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12641,10 +12645,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12681,7 +12685,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -12700,7 +12704,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12718,7 +12722,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -12738,10 +12742,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12768,7 +12772,7 @@
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12819,7 +12823,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12839,10 +12843,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12869,12 +12873,12 @@
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
@@ -12920,7 +12924,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12940,10 +12944,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13019,7 +13023,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13039,10 +13043,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13065,7 +13069,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13118,7 +13122,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13138,10 +13142,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13164,7 +13168,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13217,7 +13221,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13237,10 +13241,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13263,7 +13267,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13316,7 +13320,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13336,10 +13340,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13362,7 +13366,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13415,7 +13419,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13435,10 +13439,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13461,7 +13465,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13514,7 +13518,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13534,10 +13538,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13560,7 +13564,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13613,7 +13617,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13633,10 +13637,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13659,7 +13663,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13712,7 +13716,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13732,10 +13736,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13758,7 +13762,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13811,7 +13815,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13831,10 +13835,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13857,7 +13861,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13910,7 +13914,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13930,10 +13934,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13956,7 +13960,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14009,7 +14013,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14029,10 +14033,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14055,7 +14059,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14108,7 +14112,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14128,13 +14132,13 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>74</v>
@@ -14156,10 +14160,10 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -14211,7 +14215,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14231,10 +14235,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14332,10 +14336,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14433,10 +14437,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14534,10 +14538,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14635,10 +14639,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14738,10 +14742,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14841,10 +14845,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14944,10 +14948,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15047,10 +15051,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15148,10 +15152,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15188,7 +15192,7 @@
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15207,7 +15211,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15225,7 +15229,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -15245,10 +15249,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15275,7 +15279,7 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15326,7 +15330,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15346,10 +15350,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15376,12 +15380,12 @@
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
@@ -15427,7 +15431,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15447,10 +15451,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15526,7 +15530,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15546,10 +15550,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15572,7 +15576,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15625,7 +15629,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15645,10 +15649,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15671,7 +15675,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15724,7 +15728,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15744,10 +15748,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15770,7 +15774,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15823,7 +15827,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15843,10 +15847,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15869,7 +15873,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15922,7 +15926,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15942,10 +15946,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15968,7 +15972,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16021,7 +16025,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16041,10 +16045,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16067,7 +16071,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16120,7 +16124,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16140,10 +16144,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16166,7 +16170,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16219,7 +16223,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16239,10 +16243,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16265,7 +16269,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16318,7 +16322,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16338,10 +16342,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16364,7 +16368,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16417,7 +16421,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16437,10 +16441,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16463,7 +16467,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16516,7 +16520,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16536,10 +16540,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16562,7 +16566,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16615,7 +16619,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16635,13 +16639,13 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>74</v>
@@ -16663,10 +16667,10 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -16718,7 +16722,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16738,10 +16742,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16839,10 +16843,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16940,10 +16944,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17041,10 +17045,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17142,10 +17146,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17245,10 +17249,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17348,10 +17352,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17451,10 +17455,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17554,10 +17558,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17655,10 +17659,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17695,7 +17699,7 @@
         <v>74</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>74</v>
@@ -17714,7 +17718,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -17732,7 +17736,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -17752,10 +17756,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17782,7 +17786,7 @@
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17833,7 +17837,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17853,10 +17857,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17883,12 +17887,12 @@
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
@@ -17934,7 +17938,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17954,10 +17958,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18033,7 +18037,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18053,10 +18057,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18079,7 +18083,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18132,7 +18136,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18152,10 +18156,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18178,7 +18182,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18231,7 +18235,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18251,10 +18255,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18277,7 +18281,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18330,7 +18334,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18350,10 +18354,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18376,7 +18380,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18429,7 +18433,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18449,10 +18453,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18475,7 +18479,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18528,7 +18532,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18548,10 +18552,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18574,7 +18578,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18627,7 +18631,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18647,10 +18651,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18673,7 +18677,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18726,7 +18730,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18746,10 +18750,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18772,7 +18776,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18825,7 +18829,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -18845,10 +18849,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18871,7 +18875,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -18924,7 +18928,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18944,10 +18948,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18970,7 +18974,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19023,7 +19027,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19043,10 +19047,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19069,7 +19073,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19122,7 +19126,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19142,10 +19146,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19168,7 +19172,7 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19221,7 +19225,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19241,10 +19245,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19267,7 +19271,7 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19320,7 +19324,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19340,10 +19344,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19366,7 +19370,7 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19419,7 +19423,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccin-recommande.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
